--- a/vtiger-framework-premium/src/test/resources/testScriptData.xlsx
+++ b/vtiger-framework-premium/src/test/resources/testScriptData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
